--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="499">
   <si>
     <t>Filename</t>
   </si>
@@ -808,688 +808,709 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9979,0.0000,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.9793,0.0001,0.0002,0.0198</t>
-  </si>
-  <si>
-    <t>0.0228,0.0002,0.0005,0.9929</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0002</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9919,0.0001,0.0024,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.9922,0.0001,0.0013,0.0034</t>
+  </si>
+  <si>
+    <t>0.0524,0.0005,0.0001,0.9867</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9389,0.0031,0.0426,0.0014</t>
+  </si>
+  <si>
+    <t>0.0981,0.0012,0.9223,0.0006</t>
+  </si>
+  <si>
+    <t>0.8621,0.0041,0.1238,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0006,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.6880,0.0011,0.3012,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9992,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9935,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7669,0.0017,0.1819,0.0020</t>
+  </si>
+  <si>
+    <t>0.0069,0.0013,0.9904,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0663,0.0003,0.9632,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0003,0.9964,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.8830,0.0997,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.2682,0.0165,0.6637,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0033,0.9992,0.0027</t>
+  </si>
+  <si>
+    <t>0.0104,0.9747,0.0117,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9690,0.0364,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9985,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.5946,0.9723,0.0004</t>
+  </si>
+  <si>
+    <t>0.0058,0.0038,0.9780,0.0071</t>
+  </si>
+  <si>
+    <t>0.0009,0.0019,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0031,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9983,0.0060,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0228,0.0514,0.0004,0.9623</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.1674,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.0007,0.9948,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0047,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9995,0.0035</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9220,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9889,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9981,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0040,0.9982,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9946,0.0009,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9719,0.0037,0.0142,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9809,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9980,0.0656,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.6798,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0008,0.9989</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9883,0.3772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9529,0.9885,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9499,0.9753,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.7547,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9342,0.9676,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0022,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.9017,0.0011,0.1002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0007,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8782,0.2332,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4831,0.0023,0.4761,0.0031</t>
+  </si>
+  <si>
+    <t>0.9649,0.0031,0.0156,0.0002</t>
+  </si>
+  <si>
+    <t>0.8852,0.0059,0.0626,0.0007</t>
+  </si>
+  <si>
+    <t>0.9349,0.0018,0.0424,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.0063,0.0082,0.9842</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0225,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.0000,0.9453,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9987,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.6117,0.3597,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.5970,0.4018,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0005,0.0002</t>
   </si>
   <si>
     <t>0.9989,0.0001,0.0003,0.0002</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9518,0.0019,0.0361,0.0007</t>
-  </si>
-  <si>
-    <t>0.0308,0.0024,0.9730,0.0008</t>
-  </si>
-  <si>
-    <t>0.3171,0.0003,0.8371,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.0008,0.9931,0.0002</t>
-  </si>
-  <si>
-    <t>0.2881,0.0012,0.7508,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.9955,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4122,0.0008,0.5309,0.0057</t>
-  </si>
-  <si>
-    <t>0.6194,0.0009,0.3823,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0121,0.0017,0.9860,0.0002</t>
-  </si>
-  <si>
-    <t>0.9569,0.0001,0.0557,0.0000</t>
-  </si>
-  <si>
-    <t>0.0131,0.0007,0.9889,0.0003</t>
+    <t>0.9992,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0572,0.9874,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.7458,0.8658,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0009,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9856,0.0005,0.0077,0.0001</t>
+  </si>
+  <si>
+    <t>0.0241,0.0032,0.9759,0.0007</t>
+  </si>
+  <si>
+    <t>0.4905,0.0001,0.6708,0.0005</t>
+  </si>
+  <si>
+    <t>0.9101,0.0046,0.0648,0.0036</t>
+  </si>
+  <si>
+    <t>0.0067,0.0001,0.0005,0.9974</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9764,0.0000</t>
+  </si>
+  <si>
+    <t>0.0175,0.9828,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.1627,0.8136,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0002,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.0029,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0009,0.0071,0.9963,0.0025</t>
+  </si>
+  <si>
+    <t>0.3141,0.0003,0.0013,0.8825</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0201,0.9656,0.0049,0.0019</t>
+  </si>
+  <si>
+    <t>0.9919,0.0015,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0687,0.8913,0.0084,0.0016</t>
+  </si>
+  <si>
+    <t>0.9869,0.0017,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.9383,0.0580,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9790,0.0103,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9659,0.0192,0.0084,0.0005</t>
+  </si>
+  <si>
+    <t>0.6956,0.3033,0.0075,0.0002</t>
+  </si>
+  <si>
+    <t>0.9468,0.0321,0.0115,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0030,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9903,0.0019,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9620,0.0177,0.0063,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9656,0.0044,0.0049,0.0063</t>
+  </si>
+  <si>
+    <t>0.0018,0.0035,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0103,0.9923,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.5511,0.4836,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.8302,0.0074,0.1191,0.0009</t>
-  </si>
-  <si>
-    <t>0.0008,0.0036,0.9988,0.0010</t>
-  </si>
-  <si>
-    <t>0.0028,0.9943,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.6916,0.0152,0.1976,0.0131</t>
-  </si>
-  <si>
-    <t>0.8760,0.1708,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9966,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.6754,0.9570,0.0004</t>
-  </si>
-  <si>
-    <t>0.0060,0.0015,0.9907,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0053,0.9937,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0096,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9904,0.0125,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0085,0.0139,0.0003,0.9931</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0908,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.0060,0.0017,0.9929,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0023,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0011,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0030,0.9998,0.0010</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9448,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9993,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9813,0.0008,0.0160,0.0002</t>
-  </si>
-  <si>
-    <t>0.9797,0.0007,0.0170,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9865,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9798,0.9682,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.6575,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0008,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0006,0.9992</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.9972,0.0376,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9911,0.9638,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9701,0.8266,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9884,0.9707,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9341,0.8230,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0022,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0003,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9967,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9672,0.0573,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8624,0.0072,0.0758,0.0037</t>
-  </si>
-  <si>
-    <t>0.5641,0.0309,0.1924,0.0007</t>
-  </si>
-  <si>
-    <t>0.7879,0.0085,0.1081,0.0016</t>
-  </si>
-  <si>
-    <t>0.0727,0.0012,0.9290,0.0017</t>
-  </si>
-  <si>
-    <t>0.0005,0.0058,0.0045,0.9923</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0123,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9094,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9574,0.0380,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9610,0.0293,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0000,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0505,0.9962,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0438,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0017,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8334,0.0034,0.1319,0.0031</t>
-  </si>
-  <si>
-    <t>0.4364,0.0002,0.6979,0.0003</t>
-  </si>
-  <si>
-    <t>0.9842,0.0007,0.0067,0.0006</t>
-  </si>
-  <si>
-    <t>0.0103,0.0000,0.0001,0.9977</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9962,0.9466,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0199,0.9826,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9856,0.0084,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0020,0.0124,0.9938,0.0017</t>
-  </si>
-  <si>
-    <t>0.9750,0.0001,0.0012,0.0284</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.0204,0.9555,0.0194,0.0016</t>
-  </si>
-  <si>
-    <t>0.9914,0.0012,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0205,0.8993,0.0321,0.0037</t>
-  </si>
-  <si>
-    <t>0.9738,0.0057,0.0081,0.0003</t>
-  </si>
-  <si>
-    <t>0.9731,0.0220,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9917,0.0032,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9532,0.0264,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9680,0.0248,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.9456,0.0560,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.0370,0.0139,0.9554,0.0006</t>
-  </si>
-  <si>
-    <t>0.9935,0.0046,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9936,0.0005,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9536,0.0384,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.9700,0.0088,0.0031,0.0046</t>
-  </si>
-  <si>
-    <t>0.0102,0.0099,0.9745,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0462,0.0078,0.9350,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0003</t>
-  </si>
-  <si>
-    <t>0.0722,0.0024,0.9201,0.0008</t>
-  </si>
-  <si>
-    <t>0.0699,0.0004,0.9571,0.0001</t>
-  </si>
-  <si>
-    <t>0.0568,0.0039,0.9222,0.0082</t>
-  </si>
-  <si>
-    <t>0.4800,0.2266,0.0369,0.0002</t>
-  </si>
-  <si>
-    <t>0.0277,0.9566,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.9462,0.0077,0.0279,0.0003</t>
-  </si>
-  <si>
-    <t>0.9215,0.0036,0.0523,0.0009</t>
-  </si>
-  <si>
-    <t>0.2756,0.0098,0.6504,0.0010</t>
-  </si>
-  <si>
-    <t>0.6009,0.4405,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0848,0.9306,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9920,0.0088,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0098,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9441,0.1095,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9832,0.0118,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9884,0.0019,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.8918,0.0024,0.0712,0.0037</t>
-  </si>
-  <si>
-    <t>0.9409,0.0008,0.0519,0.0007</t>
-  </si>
-  <si>
-    <t>0.1712,0.0007,0.8958,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.1266,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0113,0.9946,0.0003</t>
-  </si>
-  <si>
-    <t>0.0048,0.0028,0.9921,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0027,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0008,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.8164,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0245,0.4001,0.3577,0.0008</t>
-  </si>
-  <si>
-    <t>0.9599,0.0054,0.0183,0.0037</t>
-  </si>
-  <si>
-    <t>0.0092,0.0015,0.9924,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0044,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0534,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0009,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0023,0.9923,0.0007</t>
-  </si>
-  <si>
-    <t>0.4773,0.0006,0.6573,0.0004</t>
-  </si>
-  <si>
-    <t>0.0691,0.0003,0.9529,0.0013</t>
-  </si>
-  <si>
-    <t>0.9724,0.0028,0.0173,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0074,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0067,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.0210,0.9755,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0005,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0071,0.0068,0.9854,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0950,0.0001,0.0045,0.9525</t>
-  </si>
-  <si>
-    <t>0.0018,0.0059,0.0024,0.9944</t>
-  </si>
-  <si>
-    <t>0.0126,0.0000,0.0001,0.9970</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0236,0.1771,0.0010,0.9509</t>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0110,0.0008,0.9883,0.0005</t>
+  </si>
+  <si>
+    <t>0.0213,0.0009,0.9819,0.0004</t>
+  </si>
+  <si>
+    <t>0.4989,0.0133,0.1312,0.1108</t>
+  </si>
+  <si>
+    <t>0.4820,0.0793,0.1537,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.0529,0.9658,0.0003</t>
+  </si>
+  <si>
+    <t>0.9059,0.0089,0.0580,0.0003</t>
+  </si>
+  <si>
+    <t>0.7989,0.0166,0.0859,0.0035</t>
+  </si>
+  <si>
+    <t>0.5637,0.0081,0.3558,0.0009</t>
+  </si>
+  <si>
+    <t>0.9565,0.0688,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.9945,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0019,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9873,0.0191,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1302,0.9329,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0019,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9738,0.0044,0.0076,0.0003</t>
+  </si>
+  <si>
+    <t>0.8026,0.0030,0.1358,0.0047</t>
+  </si>
+  <si>
+    <t>0.5633,0.0002,0.5836,0.0004</t>
+  </si>
+  <si>
+    <t>0.7067,0.0010,0.3671,0.0007</t>
+  </si>
+  <si>
+    <t>0.0025,0.0005,0.9977,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0254,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0052,0.9966,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0334,0.9877,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0077,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0169,0.1537,0.7965,0.0008</t>
+  </si>
+  <si>
+    <t>0.8697,0.0007,0.1068,0.0041</t>
+  </si>
+  <si>
+    <t>0.0026,0.0009,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0102,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0260,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0020,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.1152,0.0007,0.9416,0.0004</t>
+  </si>
+  <si>
+    <t>0.8715,0.0004,0.1727,0.0008</t>
+  </si>
+  <si>
+    <t>0.9696,0.0022,0.0164,0.0007</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0283,0.9810,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0178,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.0081,0.9884,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.0005,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.0100,0.0008,0.9885,0.0008</t>
+  </si>
+  <si>
+    <t>0.0110,0.0118,0.9698,0.0018</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.8352,0.0000,0.0008,0.3594</t>
+  </si>
+  <si>
+    <t>0.0009,0.0249,0.0015,0.9934</t>
+  </si>
+  <si>
+    <t>0.0053,0.0000,0.0005,0.9978</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.6199,0.0294,0.0071,0.2746</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1896,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1910,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1938,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2068,7 +2089,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2096,7 +2117,7 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
         <v>280</v>
@@ -2169,7 +2190,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,10 +2201,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2194,10 +2215,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,10 +2257,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,7 +2302,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2292,10 +2313,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2330,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2358,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2372,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,7 +2386,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2400,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,7 +2414,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2442,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2470,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2498,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2512,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2526,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2540,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2554,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2610,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2624,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2638,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2652,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2680,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2694,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2708,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2722,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2880,7 +2901,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>335</v>
@@ -2953,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2988,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +3002,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +3016,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,7 +3030,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3058,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,7 +3072,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3086,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,7 +3100,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>272</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>322</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3296,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3310,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>307</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3401,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3450,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3457,7 +3478,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,10 +3489,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,7 +3506,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3499,7 +3520,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3531,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3548,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3562,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3590,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3604,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3618,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3646,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>275</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3695,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3730,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3723,7 +3744,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3758,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,10 +3783,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3800,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,10 +3839,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3856,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3849,7 +3870,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3898,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3912,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3926,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,7 +3940,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3954,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3968,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3982,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,10 +3993,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +4010,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4003,7 +4024,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4052,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,10 +4063,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,7 +4094,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4115,7 +4136,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4143,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>356</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4290,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4304,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,7 +4318,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4308,10 +4329,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4346,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4360,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4388,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4416,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>357</v>
+        <v>307</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>291</v>
+        <v>434</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4514,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4542,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,10 +4553,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,10 +4567,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,10 +4581,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,7 +4598,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4612,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,10 +4623,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4640,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4654,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4668,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4682,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,10 +4693,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4738,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,10 +4749,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,10 +4763,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4808,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4822,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4836,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4920,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4934,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4938,10 +4959,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4973,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4990,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>467</v>
+        <v>307</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5074,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>328</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5088,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5102,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5116,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,10 +5127,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>380</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>356</v>
+        <v>483</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5228,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5242,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5256,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>349</v>
+        <v>461</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5340,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5354,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5368,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,10 +5379,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5410,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5424,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5438,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,10 +5449,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
